--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/334d56c47349e4dc/Desktop/TEST/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_4793790217627CBFEB7154B74C5DCE3A57CDEB96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56B1FD98-79A0-4C72-87A0-A5637F2FBFE9}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_4793790217627CBFEB7154B74C5DCE3A57CDEB96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B24E8390-E079-4995-8CAA-135D9E12A2B0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -149,13 +149,16 @@
   </si>
   <si>
     <t>15 tháng một lần.</t>
+  </si>
+  <si>
+    <t>Theo Luật PCCC 2024, "Cơ sở có nguy hiểm về cháy, nổ" được định nghĩa như thế nào?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +177,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF303030"/>
+      <name val="Google Sans Text"/>
     </font>
   </fonts>
   <fills count="3">
@@ -210,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,6 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -236,6 +245,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -524,7 +537,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -533,7 +546,7 @@
     <col min="8" max="8" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,12 +572,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
+      <c r="B2" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -585,7 +598,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="43.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -611,7 +624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="28.8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -637,7 +650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="28.8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -663,7 +676,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="28.8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -689,7 +702,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="28.8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -715,7 +728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="43.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -741,7 +754,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="28.8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -767,7 +780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="28.8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -793,7 +806,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="28.8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -819,7 +832,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="28.8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -845,7 +858,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="43.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -871,7 +884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="28.8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -897,7 +910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="28.8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -923,7 +936,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="28.8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -949,7 +962,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="28.8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -975,7 +988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="43.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1001,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1027,7 +1040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="28.8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1053,7 +1066,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="28.8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1079,7 +1092,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="28.8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1105,7 +1118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="43.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1131,7 +1144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="28.8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1157,7 +1170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="28.8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1183,7 +1196,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="28.8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1209,7 +1222,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="28.8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1235,7 +1248,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="43.2">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1261,7 +1274,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="28.8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1287,7 +1300,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="28.8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1313,7 +1326,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="28.8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1339,7 +1352,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="28.8">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1365,7 +1378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="43.2">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1391,7 +1404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="28.8">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1417,7 +1430,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="28.8">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1443,7 +1456,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="28.8">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1469,7 +1482,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="28.8">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1495,7 +1508,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="43.2">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1521,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="28.8">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1547,7 +1560,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="28.8">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1573,7 +1586,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="28.8">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1599,7 +1612,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="28.8">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1625,7 +1638,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="43.2">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1651,7 +1664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="28.8">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1677,7 +1690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="28.8">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1703,7 +1716,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="28.8">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -1729,7 +1742,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="28.8">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -1755,7 +1768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="43.2">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -1781,7 +1794,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="28.8">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -1807,7 +1820,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="28.8">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -1833,7 +1846,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="28.8">
       <c r="A51" s="2">
         <v>50</v>
       </c>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/334d56c47349e4dc/Desktop/TEST/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/334d56c47349e4dc/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_4793790217627CBFEB7154B74C5DCE3A57CDEB96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B24E8390-E079-4995-8CAA-135D9E12A2B0}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_ACE59B2693A5836F0581D66F1A4761D53D65EEA9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87F6AB77-4AEE-4DE3-8D65-154F0B515A38}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="561">
   <si>
     <t>ID</t>
   </si>
@@ -46,119 +46,1670 @@
     <t>Explanation</t>
   </si>
   <si>
-    <t>Theo Nghị định 105/2025/NĐ-CP, cơ quan Công an kiểm tra định kỳ bao lâu một lần đối với các cơ sở thuộc nhóm 1 (quy định tại Phụ lục II)?</t>
-  </si>
-  <si>
-    <t>06 tháng một lần.</t>
-  </si>
-  <si>
-    <t>01 năm một lần.</t>
-  </si>
-  <si>
-    <t>02 năm một lần.</t>
-  </si>
-  <si>
-    <t>03 năm một lần.</t>
-  </si>
-  <si>
-    <t>Căn cứ: Điểm a, Khoản 2, Điều 13 Nghị định 105/2025/NĐ-CP</t>
-  </si>
-  <si>
-    <t>Cơ quan Công an tiến hành kiểm tra đột xuất về PCCC đối với cơ sở trong trường hợp nào sau đây?</t>
-  </si>
-  <si>
-    <t>Khi cơ sở có sự thay đổi người đứng đầu.</t>
-  </si>
-  <si>
-    <t>Khi có dấu hiệu vi phạm pháp luật, có đơn khiếu nại, tố cáo về vi phạm pháp luật liên quan đến PCCC.</t>
-  </si>
-  <si>
-    <t>Khi cơ sở bắt đầu kỳ kinh doanh mới vào đầu năm.</t>
-  </si>
-  <si>
-    <t>Khi đến thời hạn bảo dưỡng hệ thống PCCC của cơ sở.</t>
-  </si>
-  <si>
-    <t>Ủy ban nhân dân cấp xã tổ chức kiểm tra định kỳ về PCCC bao lâu một lần đối với cơ sở thuộc Phụ lục I (trừ cơ sở có nguy hiểm cháy nổ tại Phụ lục II)?</t>
-  </si>
-  <si>
-    <t>Không quy định kiểm tra định kỳ, chỉ kiểm tra đột xuất.</t>
-  </si>
-  <si>
-    <t>Căn cứ: Điểm c, Khoản 2, Điều 13 Nghị định 105/2025/NĐ-CP</t>
-  </si>
-  <si>
-    <t>Trách nhiệm tự tổ chức kiểm tra PCCC thường xuyên đối với nhà ở thuộc về đối tượng nào?</t>
-  </si>
-  <si>
-    <t>Cảnh sát khu vực quản lý địa bàn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trưởng thôn, Tổ trưởng tổ dân phố. </t>
+    <t>Theo Luật PCCC năm 2024, đối tượng nào sau đây thuộc diện phải kiểm tra về phòng cháy, chữa cháy?</t>
+  </si>
+  <si>
+    <t>Cơ sở thuộc diện quản lý về PCCC.</t>
+  </si>
+  <si>
+    <t>Nhà ở, nhà ở kết hợp sản xuất, kinh doanh.</t>
+  </si>
+  <si>
+    <t>Công trình xây dựng trong quá trình thi công và phương tiện giao thông có yêu cầu về an toàn PCCC.</t>
+  </si>
+  <si>
+    <t>Tất cả các phương án trên.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1 Điều 11 Luật PCCC số 55/2024/QH15.</t>
+  </si>
+  <si>
+    <t>Theo quy định về thẩm quyền, chủ thể nào sau đây tự tổ chức kiểm tra về phòng cháy, chữa cháy đối với phạm vi quản lý của mình?</t>
   </si>
   <si>
     <t>Ủy ban nhân dân cấp xã.</t>
   </si>
   <si>
-    <t>Chủ hộ gia đình trực tiếp sử dụng nhà ở, người thuê, mượn, ở nhờ.</t>
-  </si>
-  <si>
-    <t>Căn cứ: Điểm h, Khoản 2, Điều 13 Nghị định 105/2025/NĐ-CP</t>
-  </si>
-  <si>
-    <t>Trong công tác kiểm tra định kỳ, cơ quan chủ trì thành lập Đoàn kiểm tra phải gửi văn bản thông báo cho đối tượng được kiểm tra trước bao nhiêu ngày làm việc?</t>
-  </si>
-  <si>
-    <t>Trước 01 ngày làm việc.</t>
-  </si>
-  <si>
-    <t>Trước 03 ngày làm việc.</t>
-  </si>
-  <si>
-    <t>Trước 05 ngày làm việc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trước 07 ngày làm việc. </t>
-  </si>
-  <si>
-    <t>Căn cứ: Điểm b, Khoản 3, Điều 14 Nghị định 105/2025/NĐ-CP</t>
-  </si>
-  <si>
-    <t>7 tháng một lần.</t>
-  </si>
-  <si>
-    <t>8 tháng một lần.</t>
-  </si>
-  <si>
-    <t>9 tháng một lần.</t>
-  </si>
-  <si>
-    <t>10 tháng một lần.</t>
-  </si>
-  <si>
-    <t>11 tháng một lần.</t>
-  </si>
-  <si>
-    <t>12 tháng một lần.</t>
-  </si>
-  <si>
-    <t>13 tháng một lần.</t>
-  </si>
-  <si>
-    <t>14 tháng một lần.</t>
-  </si>
-  <si>
-    <t>15 tháng một lần.</t>
-  </si>
-  <si>
-    <t>Theo Luật PCCC 2024, "Cơ sở có nguy hiểm về cháy, nổ" được định nghĩa như thế nào?</t>
+    <t>Cơ quan Công an và Cơ quan chuyên môn về xây dựng.</t>
+  </si>
+  <si>
+    <t>Người đứng đầu cơ sở, chủ hộ gia đình, chủ phương tiện giao thông, chủ đầu tư.</t>
+  </si>
+  <si>
+    <t>Cơ quan đăng kiểm.</t>
+  </si>
+  <si>
+    <t>Người đứng đầu cơ sở có trách nhiệm nào sau đây về PCCC và CNCH?</t>
+  </si>
+  <si>
+    <t>Tổ chức tuyên truyền, huấn luyện nghiệp vụ PCCC, CNCH cho các đối tượng thuộc phạm vi quản lý.</t>
+  </si>
+  <si>
+    <t>Ban hành hoặc tham mưu ban hành nội quy PCCC, CNCH.</t>
+  </si>
+  <si>
+    <t>Thành lập, duy trì hoạt động Đội PCCC cơ sở hoặc Đội PCCC chuyên ngành theo quy định.</t>
+  </si>
+  <si>
+    <t>Tất cả các đáp án trên đều đúng.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Các điểm a, b, c thuộc Khoản 3 Điều 8 Luật PCCC số 55/2024/QH15.</t>
+  </si>
+  <si>
+    <t>Khi kiểm tra điều kiện an toàn phòng cháy đối với công trình xây dựng đang trong quá trình thi công, yêu cầu nào sau đây là BẮT BUỘC?</t>
+  </si>
+  <si>
+    <t>Có nội quy phòng cháy, chữa cháy, cứu nạn, cứu hộ phù hợp với tính chất, đặc điểm của công trình.</t>
+  </si>
+  <si>
+    <t>Trang bị phương tiện hoặc hệ thống PCCC phù hợp với tính chất công trình theo quy định về an toàn thi công.</t>
+  </si>
+  <si>
+    <t>Có phân công người thực hiện nhiệm vụ PCCC, CNCH thuộc phạm vi quản lý.</t>
+  </si>
+  <si>
+    <t>Tất cả các yêu cầu trên.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1 Điều 19 Luật PCCC số 55/2024/QH15.</t>
+  </si>
+  <si>
+    <t>Khi kiểm tra việc chấp hành quy định an toàn PCCC đối với "Nhà ở kết hợp sản xuất, kinh doanh hàng hóa nguy hiểm về cháy, nổ", cán bộ kiểm tra cần xác định yếu tố nào sau đây?</t>
+  </si>
+  <si>
+    <t>Có được phép bố trí chỗ ngủ cho nhân viên trực đêm trong khu vực sản xuất hay không.</t>
+  </si>
+  <si>
+    <t>Khu vực sản xuất, kinh doanh hàng hóa nguy hiểm về cháy, nổ có được ngăn cháy với lối thoát nạn của khu vực để ở hay không.</t>
+  </si>
+  <si>
+    <t>Chủ nhà có quyền tự ý chuyển đổi thêm công năng để chứa hóa chất nổ mà không cần thẩm định hay không.</t>
+  </si>
+  <si>
+    <t>Chỉ cần trang bị 01 bình chữa cháy xách tay là đủ điều kiện an toàn.</t>
+  </si>
+  <si>
+    <t>Hành vi nào sau đây bị pháp luật NGHIÊM CẤM trong công tác thẩm định, kiểm tra nghiệm thu về PCCC?</t>
+  </si>
+  <si>
+    <t>Làm giả, làm sai lệch kết quả thẩm định thiết kế về phòng cháy và chữa cháy, kết quả kiểm tra nghiệm thu về phòng cháy và chữa cháy.</t>
+  </si>
+  <si>
+    <t>Phạt vi phạm hành chính đối với công trình chưa có văn bản thẩm định mà đã thi công.</t>
+  </si>
+  <si>
+    <t>Yêu cầu chủ đầu tư tổ chức thực tập phương án chữa cháy.</t>
+  </si>
+  <si>
+    <t>Chuyển đổi công năng sử dụng công trình khi đã bảo đảm an toàn PCCC và pháp luật cho phép.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 5 Điều 14 Luật PCCC số 55/2024/QH15.</t>
+  </si>
+  <si>
+    <t>Theo quy định về kiểm tra công tác nghiệm thu, đối với các bộ phận của công trình bị che khuất thì việc nghiệm thu về PCCC phải được thực hiện khi nào?</t>
+  </si>
+  <si>
+    <t>Sau khi hoàn thành toàn bộ dự án và đưa vào sử dụng.</t>
+  </si>
+  <si>
+    <t>Có thể bỏ qua nếu đã thẩm định thiết kế.</t>
+  </si>
+  <si>
+    <t>Trước khi tiến hành các bước thi công tiếp theo.</t>
+  </si>
+  <si>
+    <t>Cùng thời điểm với lúc nghiệm thu bàn giao hệ thống báo cháy.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b, Khoản 2 Điều 18 Luật PCCC số 55/2024/QH15.</t>
+  </si>
+  <si>
+    <t>Trong trường hợp xảy ra cháy tại cơ sở, lực lượng Công an chưa kịp đến hiện trường, ai là người có thẩm quyền cao nhất chỉ huy chữa cháy?</t>
+  </si>
+  <si>
+    <t>Trưởng thôn, Tổ trưởng tổ dân phố nơi cơ sở đóng quân.</t>
+  </si>
+  <si>
+    <t>Bất kỳ người dân nào phát hiện đám cháy đầu tiên.</t>
+  </si>
+  <si>
+    <t>Người đứng đầu cơ sở; trường hợp vắng mặt thì Đội trưởng Đội PCCC cơ sở/chuyên ngành hoặc người được ủy quyền là người chỉ huy chữa cháy.</t>
+  </si>
+  <si>
+    <t>Lực lượng y tế hoặc điện lực có mặt sớm nhất.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a, Khoản 2 Điều 28 Luật PCCC số 55/2024/QH15.</t>
+  </si>
+  <si>
+    <t>Theo Nghị định 105/2025/NĐ-CP, nội quy phòng cháy, chữa cháy, cứu nạn, cứu hộ đối với cơ sở bắt buộc phải gồm nội dung cơ bản nào sau đây?</t>
+  </si>
+  <si>
+    <t>Quy định mức khen thưởng cho lực lượng dân phòng khi tham gia chữa cháy.</t>
+  </si>
+  <si>
+    <t>Quy định về chế độ mua bảo hiểm cháy nổ cho toàn bộ nhân viên.</t>
+  </si>
+  <si>
+    <t>Quy định việc quản lý, sử dụng điện, nguồn lửa, nguồn nhiệt, thiết bị, dụng cụ sinh lửa, sinh nhiệt, chất dễ cháy, nổ.</t>
+  </si>
+  <si>
+    <t>Quy định việc bồi thường thiệt hại cho các hộ dân xung quanh khi xảy ra cháy lan.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a, Khoản 1, Điều 3 Nghị định 105/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Trong bộ hồ sơ quản lý về PCCC của cơ sở, tài liệu nào sau đây phải được lưu trữ tối thiểu 05 năm kể từ năm lập, ban hành?</t>
+  </si>
+  <si>
+    <t>Phiếu thông tin của cơ sở (Mẫu số PC01).</t>
+  </si>
+  <si>
+    <t>Quyết định thành lập Đội phòng cháy, chữa cháy cơ sở.</t>
+  </si>
+  <si>
+    <t>Biên bản tự kiểm tra về phòng cháy, chữa cháy của cơ sở (Mẫu số PC02).</t>
+  </si>
+  <si>
+    <t>Phương án chữa cháy của cơ sở (Mẫu số PC06).</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 4, Điều 4 Nghị định 105/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Trong quá trình sử dụng, trường hợp cải tạo nào sau đây đối với công trình (thuộc diện phải thẩm định) BẮT BUỘC phải thực hiện thẩm định lại thiết kế về PCCC?</t>
+  </si>
+  <si>
+    <t>Thay đổi màu sơn mặt ngoài và thay gạch lát nền của công trình.</t>
+  </si>
+  <si>
+    <t>Thay đổi các thiết bị chiếu sáng thông thường để tiết kiệm điện.</t>
+  </si>
+  <si>
+    <t>Tăng số tầng; hoặc tăng diện tích xây dựng dẫn đến thay đổi yêu cầu về giải pháp phân chia khoang cháy.</t>
+  </si>
+  <si>
+    <t>Thay đổi người đứng đầu (Giám đốc) cơ sở kinh doanh.</t>
+  </si>
+  <si>
+    <t>Theo quy định, cơ quan Công an có thẩm quyền tiến hành kiểm tra định kỳ về phòng cháy, chữa cháy bao lâu một lần đối với cơ sở thuộc nhóm 1 (quy định tại Phụ lục II)?</t>
+  </si>
+  <si>
+    <t>Định kỳ 06 tháng một lần.</t>
+  </si>
+  <si>
+    <t>Định kỳ 01 năm một lần.</t>
+  </si>
+  <si>
+    <t>Định kỳ 02 năm một lần.</t>
+  </si>
+  <si>
+    <t>Định kỳ 03 năm một lần.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a, Khoản 2, Điều 13 Nghị định 105/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Người đứng đầu cơ sở có nguy hiểm về cháy, nổ (thuộc Phụ lục II) phải gửi Báo cáo kết quả thực hiện công tác PCCC (Mẫu PC04) cho cơ quan quản lý định kỳ vào thời gian nào?</t>
+  </si>
+  <si>
+    <t>Trước ngày 15 tháng 6 và trước ngày 15 tháng 12 hằng năm.</t>
+  </si>
+  <si>
+    <t>Trước ngày 30 tháng 6 và trước ngày 31 tháng 12 hằng năm.</t>
+  </si>
+  <si>
+    <t>Chỉ báo cáo 01 lần trước ngày 15 tháng 12 hằng năm.</t>
+  </si>
+  <si>
+    <t>Báo cáo hàng quý vào trước ngày 15 của tháng đầu quý tiếp theo.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 2, Điều 14 Nghị định 105/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Chủ thể nào có thẩm quyền tổ chức xây dựng và phê duyệt Phương án chữa cháy, cứu nạn, cứu hộ của cơ sở (Mẫu số PC06)?</t>
+  </si>
+  <si>
+    <t>Trưởng Công an cấp huyện nơi cơ sở đóng quân.</t>
+  </si>
+  <si>
+    <t>Chủ tịch Ủy ban nhân dân cấp xã.</t>
+  </si>
+  <si>
+    <t>Người đứng đầu cơ sở.</t>
+  </si>
+  <si>
+    <t>Trưởng phòng Cảnh sát PCCC và CNCH Công an cấp tỉnh.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1, Điều 15 Nghị định 105/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Đối với cơ sở có từ 20 người đến 50 người thường xuyên làm việc, số lượng thành viên tối thiểu cần bố trí để tham gia Đội PCCC và CNCH cơ sở là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Tối thiểu 05 người (gồm 01 Đội trưởng).</t>
+  </si>
+  <si>
+    <t>Tối thiểu 10 người (trong đó có 01 Đội trưởng, 01 Đội phó).</t>
+  </si>
+  <si>
+    <t>Tối thiểu 15 người (trong đó có 01 Đội trưởng, 02 Đội phó).</t>
+  </si>
+  <si>
+    <t>Tối thiểu 25 người.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a, Khoản 5, Điều 20 Nghị định 105/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Thời gian huấn luyện nghiệp vụ phòng cháy, chữa cháy, cứu nạn, cứu hộ (áp dụng cho huấn luyện lần đầu) đối với thành viên Đội PCCC cơ sở được quy định như thế nào?</t>
+  </si>
+  <si>
+    <t>Tối thiểu 04 giờ và không quá 08 giờ.</t>
+  </si>
+  <si>
+    <t>Tối thiểu 08 giờ và không quá 12 giờ.</t>
+  </si>
+  <si>
+    <t>Tối thiểu 16 giờ và không quá 24 giờ.</t>
+  </si>
+  <si>
+    <t>Tối thiểu 24 giờ và không quá 32 giờ.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a, Khoản 1, Điều 29 Nghị định 105/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Theo Thông tư 36/2025/TT-BCA, chủ thể nào có trách nhiệm trang bị phương tiện phòng cháy, chữa cháy, cứu nạn, cứu hộ cho lực lượng dân phòng?</t>
+  </si>
+  <si>
+    <t>Bộ Công an.</t>
+  </si>
+  <si>
+    <t>Công an cấp huyện.</t>
+  </si>
+  <si>
+    <t>Trưởng thôn, Tổ trưởng tổ dân phố.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 2 Điều 3 - Thông tư 36/2025/TT-BCA.</t>
+  </si>
+  <si>
+    <t>Nhà, kho để phương tiện phòng cháy, chữa cháy, cứu nạn, cứu hộ phải bảo đảm các yêu cầu cơ bản nào sau đây?</t>
+  </si>
+  <si>
+    <t>Phải xây dựng ngầm dưới lòng đất để tránh cháy lan.</t>
+  </si>
+  <si>
+    <t>Phải có mái che, tường bao quanh, bảo đảm khô ráo, thoáng khí, sạch sẽ, an ninh, trật tự và có hệ thống chiếu sáng.</t>
+  </si>
+  <si>
+    <t>Bắt buộc phải có hệ thống điều hòa nhiệt độ hoạt động 24/24.</t>
+  </si>
+  <si>
+    <t>Phải đặt ngay sát nguồn nước tự nhiên (sông, hồ).</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a Khoản 1 Điều 5 - Thông tư 36/2025/TT-BCA.</t>
+  </si>
+  <si>
+    <t>Việc thống kê, báo cáo công tác quản lý, bảo quản, bảo dưỡng phương tiện phòng cháy, chữa cháy, cứu nạn, cứu hộ được thực hiện bằng hình thức nào?</t>
+  </si>
+  <si>
+    <t>Lập thành một báo cáo riêng biệt nộp về Bộ Công an hàng quý.</t>
+  </si>
+  <si>
+    <t>Được lồng ghép trong Báo cáo kết quả thực hiện công tác phòng cháy, chữa cháy, cứu nạn, cứu hộ của cơ sở (theo Mẫu số PC04).</t>
+  </si>
+  <si>
+    <t>Báo cáo trực tiếp bằng miệng cho Cảnh sát khu vực định kỳ hàng tháng.</t>
+  </si>
+  <si>
+    <t>Chỉ cần ghi vào sổ theo dõi nội bộ, không cần báo cáo.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điều 7 - Thông tư 36/2025/TT-BCA.</t>
+  </si>
+  <si>
+    <t>Trách nhiệm bảo đảm kinh phí phục vụ công tác quản lý, bảo quản, bảo dưỡng phương tiện PCCC, CNCH do hộ gia đình tự trang bị thuộc về ai?</t>
+  </si>
+  <si>
+    <t>Ngân sách nhà nước.</t>
+  </si>
+  <si>
+    <t>Lực lượng dân phòng tại khu dân cư.</t>
+  </si>
+  <si>
+    <t>Chủ hộ gia đình, cá nhân quy định tại khoản 2 Điều 43 Luật PCCC.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 2 Điều 8 - Thông tư 36/2025/TT-BCA.</t>
+  </si>
+  <si>
+    <t>Cơ quan nào chịu trách nhiệm chủ trì, biên soạn tài liệu huấn luyện, bồi dưỡng nghiệp vụ phòng cháy, chữa cháy, cứu nạn, cứu hộ và phát hành đến Công an các đơn vị, địa phương?</t>
+  </si>
+  <si>
+    <t>Công an cấp tỉnh.</t>
+  </si>
+  <si>
+    <t>Cục Cảnh sát phòng cháy, chữa cháy và cứu nạn, cứu hộ.</t>
+  </si>
+  <si>
+    <t>Trường Đại học Phòng cháy chữa cháy.</t>
+  </si>
+  <si>
+    <t>Bộ Giáo dục và Đào tạo.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1 Điều 13 - Thông tư 36/2025/TT-BCA.</t>
+  </si>
+  <si>
+    <t>Theo danh mục tại Phụ lục I, một Đội dân phòng được trang bị định mức tối thiểu bao nhiêu bình bột chữa cháy xách tay (có khối lượng chất chữa cháy không nhỏ hơn 04 kg)?</t>
+  </si>
+  <si>
+    <t>02 bình.</t>
+  </si>
+  <si>
+    <t>03 bình.</t>
+  </si>
+  <si>
+    <t>05 bình.</t>
+  </si>
+  <si>
+    <t>10 bình.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Số thứ tự 1, Phụ lục I - Danh mục, số lượng phương tiện PCCC trang bị cho lực lượng dân phòng.</t>
+  </si>
+  <si>
+    <t>Khi bảo dưỡng máy bơm chữa cháy (kiểm tra hoạt động động cơ), thời gian khởi động tối đa trong trường hợp máy bơm KHÔNG phun, hút nước là bao lâu?</t>
+  </si>
+  <si>
+    <t>Tối đa 01 phút.</t>
+  </si>
+  <si>
+    <t>Tối đa 03 phút.</t>
+  </si>
+  <si>
+    <t>Tối đa 05 phút.</t>
+  </si>
+  <si>
+    <t>Tối đa 15 phút.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b, mục 1.1, Phần II, Phụ lục II - Thông tư 36/2025/TT-BCA.</t>
+  </si>
+  <si>
+    <t>Trưởng phòng Cảnh sát PCCC và CNCH được phân công phụ trách, thực hiện công tác kiểm tra về phòng cháy, chữa cháy bắt buộc phải có thời gian thực hiện công tác PCCC, CNCH trong Công an nhân dân tối thiểu là bao nhiêu năm?</t>
+  </si>
+  <si>
+    <t>01 năm</t>
+  </si>
+  <si>
+    <t>02 năm</t>
+  </si>
+  <si>
+    <t>03 năm</t>
+  </si>
+  <si>
+    <t>05 năm</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a Khoản 3 Điều 17 Thông tư 37/2025/TT-BCA</t>
+  </si>
+  <si>
+    <t>Đối tượng quy định là Trưởng phòng, Phó Trưởng phòng thuộc Cục Cảnh sát PCCC và CNCH được phân công thực hiện công tác kiểm tra về phòng cháy, chữa cháy có thời gian bồi dưỡng nghiệp vụ hằng năm tối thiểu là bao nhiêu giờ?</t>
+  </si>
+  <si>
+    <t>08 giờ</t>
+  </si>
+  <si>
+    <t>16 giờ</t>
+  </si>
+  <si>
+    <t>24 giờ</t>
+  </si>
+  <si>
+    <t>40 giờ</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 2 Điều 20 Thông tư 37/2025/TT-BCA</t>
+  </si>
+  <si>
+    <t>Khi lập kế hoạch kiểm tra định kỳ đối với cơ sở có nguy hiểm về cháy, nổ thuộc phạm vi quản lý của năm kế tiếp, Phòng Cảnh sát PCCC và CNCH phải ban hành kế hoạch trước thời gian nào hằng năm?</t>
+  </si>
+  <si>
+    <t>Trước ngày 15 tháng 11</t>
+  </si>
+  <si>
+    <t>Trước ngày 30 tháng 11</t>
+  </si>
+  <si>
+    <t>Trước ngày 15 tháng 12</t>
+  </si>
+  <si>
+    <t>Trước ngày 31 tháng 12</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a Khoản 1 Điều 28 Thông tư 37/2025/TT-BCA</t>
+  </si>
+  <si>
+    <t>Theo Nghị định 68/2025/NĐ-CP, nếu một hành vi vi phạm hành chính có 01 tình tiết giảm nhẹ thì mức tiền phạt cụ thể được xác định như thế nào?</t>
+  </si>
+  <si>
+    <t>Áp dụng mức tối thiểu của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Xác định trong khoảng từ trên mức tối thiểu đến dưới mức trung bình của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Áp dụng mức trung bình của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Bằng 50% mức tối đa của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 4 Điều 1 Nghị định 68/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Nếu một hành vi vi phạm hành chính có từ 02 tình tiết giảm nhẹ trở lên (và không có tình tiết tăng nặng), cơ quan chức năng sẽ áp dụng mức tiền phạt nào?</t>
+  </si>
+  <si>
+    <t>Mức tối thiểu của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Mức trung bình của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Dưới mức tối thiểu của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Mức tối đa của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Khi xác định mức phạt tiền đối với một hành vi vi phạm hành chính, nếu vừa có tình tiết tăng nặng, vừa có tình tiết giảm nhẹ thì nguyên tắc áp dụng là gì?</t>
+  </si>
+  <si>
+    <t>Ưu tiên áp dụng tình tiết giảm nhẹ.</t>
+  </si>
+  <si>
+    <t>Phạt ở mức trung bình của khung tiền phạt.</t>
+  </si>
+  <si>
+    <t>Giảm trừ một tình tiết tăng nặng với một tình tiết giảm nhẹ.</t>
+  </si>
+  <si>
+    <t>Ưu tiên áp dụng tình tiết tăng nặng để răn đe.</t>
+  </si>
+  <si>
+    <t>Trừ các trường hợp có nhiều tình tiết phức tạp hoặc phải giám định, thời hạn thông thường để lập biên bản vi phạm hành chính là bao lâu kể từ khi phát hiện vi phạm?</t>
+  </si>
+  <si>
+    <t>Trong vòng 24 giờ.</t>
+  </si>
+  <si>
+    <t>Trong thời hạn 02 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Trong thời hạn 03 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Trong thời hạn 05 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 6 Điều 1 Nghị định 68/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Đối với vụ việc vi phạm hành chính có nhiều tình tiết phức tạp, phạm vi rộng, ảnh hưởng đến quyền và lợi ích hợp pháp của cá nhân, tổ chức thì thời hạn lập biên bản vi phạm hành chính là bao lâu?</t>
+  </si>
+  <si>
+    <t>Trong thời hạn 07 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Trong thời hạn 10 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Trường hợp vi phạm hành chính phải giám định, kiểm nghiệm để xác định đối tượng vi phạm, thì biên bản vi phạm hành chính được lập trong thời hạn bao lâu kể từ ngày nhận được kết quả giám định, kiểm nghiệm?</t>
+  </si>
+  <si>
+    <t>Trường hợp hành vi vi phạm có áp dụng hình thức phạt tịch thu tang vật, phương tiện, nhưng tang vật đã bị tiêu thụ, tẩu tán trái quy định pháp luật thì người vi phạm phải chịu biện pháp xử lý nào?</t>
+  </si>
+  <si>
+    <t>Buộc khôi phục lại tình trạng ban đầu.</t>
+  </si>
+  <si>
+    <t>Buộc nộp lại số tiền bằng với giá trị tang vật, phương tiện vi phạm.</t>
+  </si>
+  <si>
+    <t>Phạt tiền gấp đôi giá trị tang vật.</t>
+  </si>
+  <si>
+    <t>Chuyển hồ sơ sang cơ quan điều tra hình sự.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a Khoản 1 Điều 1 Nghị định 68/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Khi áp dụng hình thức xử phạt tước quyền sử dụng giấy phép có thời hạn, nếu có 01 tình tiết tăng nặng thì thời hạn tước quyền sử dụng giấy phép được xác định như thế nào?</t>
+  </si>
+  <si>
+    <t>Bằng mức tối đa của khung thời gian tước.</t>
+  </si>
+  <si>
+    <t>Bằng mức trung bình của khung thời gian tước.</t>
+  </si>
+  <si>
+    <t>Trong khoảng từ trên mức trung bình đến dưới mức tối đa của khung thời gian tước.</t>
+  </si>
+  <si>
+    <t>Tước vĩnh viễn giấy phép.</t>
+  </si>
+  <si>
+    <t>Người đã ban hành quyết định xử phạt vi phạm hành chính tự mình hoặc theo yêu cầu có trách nhiệm "đính chính" quyết định trong trường hợp nào?</t>
+  </si>
+  <si>
+    <t>Khi phát hiện hành vi vi phạm thực tế khác với biên bản.</t>
+  </si>
+  <si>
+    <t>Khi áp dụng sai hình thức xử phạt.</t>
+  </si>
+  <si>
+    <t>Khi có sai sót về kỹ thuật soạn thảo.</t>
+  </si>
+  <si>
+    <t>Khi người vi phạm nộp tiền chậm.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 8 Điều 1 Nghị định 68/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Theo Phụ lục ban hành kèm theo Nghị định 68/2025/NĐ-CP, ký hiệu mẫu văn bản "MQĐ01" được sử dụng cho loại hình quyết định nào?</t>
+  </si>
+  <si>
+    <t>Quyết định xử phạt vi phạm hành chính.</t>
+  </si>
+  <si>
+    <t>Quyết định xử phạt vi phạm hành chính không lập biên bản.</t>
+  </si>
+  <si>
+    <t>Quyết định cưỡng chế buộc thực hiện biện pháp khắc phục hậu quả.</t>
+  </si>
+  <si>
+    <t>Quyết định đính chính quyết định trong xử phạt vi phạm hành chính.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Bảng phụ lục ban hành kèm theo Nghị định số 68/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Theo Nghị định 189/2025/NĐ-CP, Chủ tịch Ủy ban nhân dân cấp xã có thẩm quyền phạt tiền đến mức nào đối với lĩnh vực tương ứng?</t>
+  </si>
+  <si>
+    <t>Đến 20% mức tiền phạt tối đa.</t>
+  </si>
+  <si>
+    <t>Đến 30% mức tiền phạt tối đa.</t>
+  </si>
+  <si>
+    <t>Đến 50% mức tiền phạt tối đa.</t>
+  </si>
+  <si>
+    <t>Đến 80% mức tiền phạt tối đa.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 1 Điều 5 Nghị định 189/2025/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Chủ tịch Ủy ban nhân dân cấp tỉnh có thẩm quyền phạt tiền như thế nào đối với các hành vi vi phạm hành chính?</t>
+  </si>
+  <si>
+    <t>Đến mức tối đa đối với lĩnh vực tương ứng.</t>
+  </si>
+  <si>
+    <t>Phạt tiền không giới hạn mức tối đa.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 2 Điều 5 Nghị định 189/2025/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Chánh Thanh tra Công an cấp tỉnh có thẩm quyền phạt tiền đến mức nào đối với lĩnh vực tương ứng?</t>
+  </si>
+  <si>
+    <t>Đến mức tối đa.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 3 Điều 7 Nghị định 189/2025/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Chiến sĩ Công an nhân dân đang thi hành công vụ có thẩm quyền xử phạt vi phạm hành chính với hình thức phạt tiền đến mức nào?</t>
+  </si>
+  <si>
+    <t>Đến 5% mức tiền phạt tối đa.</t>
+  </si>
+  <si>
+    <t>Đến 10% mức tiền phạt tối đa.</t>
+  </si>
+  <si>
+    <t>Đến 15% mức tiền phạt tối đa.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 1 Điều 8 Nghị định 189/2025/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Trưởng Công an cấp xã có thẩm quyền phạt tiền đến mức nào trong các lĩnh vực quản lý nhà nước tương ứng?</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 4 Điều 8 Nghị định 189/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Giám đốc Công an cấp tỉnh có thẩm quyền áp dụng mức phạt tiền như thế nào đối với các hành vi vi phạm hành chính thuộc thẩm quyền?</t>
+  </si>
+  <si>
+    <t>Chỉ được phạt tiền đến 100.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 7 Điều 8 Nghị định 189/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Trường hợp biên bản vi phạm hành chính được lập tại vùng sâu, vùng xa, biên giới, miền núi, hải đảo mà việc đi lại gặp khó khăn thì thời hạn chuyển biên bản cho người có thẩm quyền xử phạt là bao lâu?</t>
+  </si>
+  <si>
+    <t>Không quá 02 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Không quá 03 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Không quá 05 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Không quá 07 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 4 Điều 1 Nghị định 190/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Trường hợp vi phạm hành chính xảy ra trên tàu bay, tàu biển, tàu hỏa, biên bản vi phạm phải được chuyển cho người có thẩm quyền xử phạt trong thời hạn bao lâu kể từ ngày vào đến bờ hoặc cảng, nhà ga?</t>
+  </si>
+  <si>
+    <t>02 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>03 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>05 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>07 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Khi gửi quyết định xử phạt qua dịch vụ bưu chính bằng hình thức bảo đảm, nếu bưu chính từ chối phát hoặc trả lại vì lý do khách quan thì người có trách nhiệm gửi phải xử lý thế nào?</t>
+  </si>
+  <si>
+    <t>Quyết định được tự động hủy bỏ do không thể tống đạt.</t>
+  </si>
+  <si>
+    <t>Lập tức chuyển sang hình thức niêm yết công khai.</t>
+  </si>
+  <si>
+    <t>Mặc nhiên coi như người vi phạm đã nhận được quyết định.</t>
+  </si>
+  <si>
+    <t>Có trách nhiệm chuyển sang hình thức gửi khác theo quy định.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 5 Điều 1 Nghị định 190/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Quyết định xử phạt vi phạm hành chính được coi là "đã giao" cho người vi phạm khi hết thời hạn bao nhiêu ngày kể từ ngày cơ quan có thẩm quyền nhận được quyết định bị trả lại lần thứ ba qua dịch vụ bưu chính bằng hình thức bảo đảm?</t>
+  </si>
+  <si>
+    <t>Hết 03 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Hết 05 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Hết 07 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Hết 10 ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Khi áp dụng phương thức xử lý vi phạm hành chính trên môi trường điện tử, người vi phạm sử dụng chữ ký số phải đáp ứng điều kiện theo quy định của pháp luật nào?</t>
+  </si>
+  <si>
+    <t>Pháp luật về xử lý vi phạm hành chính.</t>
+  </si>
+  <si>
+    <t>Pháp luật về an toàn thông tin mạng.</t>
+  </si>
+  <si>
+    <t>Pháp luật về an ninh mạng.</t>
+  </si>
+  <si>
+    <t>Pháp luật về giao dịch điện tử.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 9 Điều 1 Nghị định 190/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Trong thủ tục xử phạt điện tử, nếu người vi phạm (cá nhân, đại diện tổ chức) không sử dụng được chữ ký số thì có thể sử dụng phương tiện xác thực nào để thay thế nhằm xác định danh tính?</t>
+  </si>
+  <si>
+    <t>Xác thực bằng chữ ký quét (scan) đính kèm qua email.</t>
+  </si>
+  <si>
+    <t>Phương tiện xác thực yếu tố về sinh trắc học bằng ảnh khuôn mặt hoặc vân tay.</t>
+  </si>
+  <si>
+    <t>Xác thực bằng tin nhắn SMS (OTP) gửi về số điện thoại cá nhân.</t>
+  </si>
+  <si>
+    <t>Xác thực qua việc gửi bản photocopy Căn cước công dân.</t>
+  </si>
+  <si>
+    <t>Thời điểm các biên bản, quyết định xử lý vi phạm hành chính trên môi trường điện tử được coi là ĐÃ gửi, nhận hợp lệ trong hệ thống thông tin ghi nhận trong trường hợp nào sau đây?</t>
+  </si>
+  <si>
+    <t>Ngay khi cơ quan chức năng bấm nút "gửi" trên phần mềm.</t>
+  </si>
+  <si>
+    <t>Khi hệ thống báo "đã gửi tin nhắn SMS" đến người vi phạm.</t>
+  </si>
+  <si>
+    <t>Khi người vi phạm đã truy cập, tải về hoặc mở biên bản, quyết định trong hệ thống.</t>
+  </si>
+  <si>
+    <t>Sau 48 giờ kể từ lúc văn bản được đưa lên Cổng dịch vụ công.</t>
+  </si>
+  <si>
+    <t>Theo quy định hiện hành tại Phụ lục của Nghị định 190/2025/NĐ-CP, Mẫu biên bản số 05 có tên gọi chính thức là gì?</t>
+  </si>
+  <si>
+    <t>Biên bản vi phạm hành chính.</t>
+  </si>
+  <si>
+    <t>Biên bản tạm giữ tang vật, phương tiện vi phạm.</t>
+  </si>
+  <si>
+    <t>Biên bản giải trình vi phạm hành chính.</t>
+  </si>
+  <si>
+    <t>Biên bản xác minh tình tiết của vụ việc vi phạm hành chính.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Phụ lục Mẫu biên bản ban hành kèm theo Nghị định số 190/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Nghị định số 190/2025/NĐ-CP (Sửa đổi, bổ sung Nghị định số 118/2021/NĐ-CP về xử lý vi phạm hành chính) chính thức có hiệu lực thi hành từ ngày tháng năm nào?</t>
+  </si>
+  <si>
+    <t>Từ ngày 01 tháng 01 năm 2025.</t>
+  </si>
+  <si>
+    <t>Từ ngày 18 tháng 03 năm 2025.</t>
+  </si>
+  <si>
+    <t>Từ ngày 01 tháng 06 năm 2025.</t>
+  </si>
+  <si>
+    <t>Từ ngày 01 tháng 07 năm 2025.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1, Điều 4 Nghị định 190/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Theo Nghị định 106/2025/NĐ-CP, thời hiệu xử phạt vi phạm hành chính trong lĩnh vực phòng cháy, chữa cháy và cứu nạn, cứu hộ là bao lâu?</t>
+  </si>
+  <si>
+    <t>06 tháng.</t>
+  </si>
+  <si>
+    <t>01 năm.</t>
+  </si>
+  <si>
+    <t>02 năm.</t>
+  </si>
+  <si>
+    <t>03 năm.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1 Điều 5 Nghị định 106/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Mức phạt tiền tối đa trong lĩnh vực phòng cháy, chữa cháy và cứu nạn, cứu hộ đối với hành vi vi phạm của TỔ CHỨC là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>50.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>80.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>100.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>150.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1 Điều 4 Nghị định 106/2025/NĐ-CP</t>
+  </si>
+  <si>
+    <t>Cơ sở có nguy hiểm về cháy, nổ thuộc nhóm 1 có hành vi KHÔNG mua bảo hiểm cháy, nổ bắt buộc thì bị phạt tiền ở mức nào?</t>
+  </si>
+  <si>
+    <t>10.000.000 đồng đến 15.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>20.000.000 đồng đến 30.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>30.000.000 đồng đến 40.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>40.000.000 đồng đến 50.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a Khoản 4 Điều 17 Nghị định 106/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Quá trình kiểm tra an toàn PCCC, nếu phát hiện cơ sở có hành vi "Khóa cửa đi lắp đặt trên lối thoát nạn hoặc đường thoát nạn", cán bộ kiểm tra sẽ lập biên bản với khung tiền phạt nào sau đây?</t>
+  </si>
+  <si>
+    <t>1.000.000 đồng đến 3.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>5.000.000 đồng đến 10.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 3 Điều 24 Nghị định 106/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Cơ sở thuộc diện quản lý về PCCC có dưới 20 người thường xuyên làm việc nhưng "Không phân công người thực hiện nhiệm vụ phòng cháy, chữa cháy, cứu nạn, cứu hộ" thì bị xử phạt như thế nào?</t>
+  </si>
+  <si>
+    <t>Phạt tiền từ 3.000.000 đồng đến 5.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Phạt tiền từ 6.000.000 đồng đến 8.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Phạt tiền từ 8.000.000 đồng đến 10.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Phạt tiền từ 10.000.000 đồng đến 20.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a Khoản 2 Điều 8 Nghị định 106/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Hành vi "Hàn, cắt kim loại mà không có biện pháp phòng cháy, chữa cháy theo quy định" bị xử phạt tiền ở mức nào?</t>
+  </si>
+  <si>
+    <t>15.000.000 đồng đến 20.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>20.000.000 đồng đến 25.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 2 Điều 11 Nghị định 106/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Đối với hành vi "Không trang bị, lắp đặt hệ thống báo cháy", mức tiền phạt quy định đối với cá nhân là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm a Khoản 9 Điều 20 Nghị định 106/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Cơ sở có hành vi gửi Báo cáo kết quả thực hiện công tác phòng cháy, chữa cháy, cứu nạn, cứu hộ "Không đúng thời hạn" sẽ bị xử phạt tiền ở mức nào?</t>
+  </si>
+  <si>
+    <t>3.000.000 đồng đến 5.000.000 đồng.</t>
+  </si>
+  <si>
+    <t>Không bị phạt tiền, chỉ phạt cảnh cáo.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b Khoản 1 Điều 10 Nghị định 106/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Nghị định số 106/2025/NĐ-CP quy định xử phạt vi phạm hành chính trong lĩnh vực phòng cháy, chữa cháy và cứu nạn, cứu hộ có hiệu lực thi hành từ ngày tháng năm nào?</t>
+  </si>
+  <si>
+    <t>01 tháng 01 năm 2025.</t>
+  </si>
+  <si>
+    <t>15 tháng 05 năm 2025.</t>
+  </si>
+  <si>
+    <t>01 tháng 07 năm 2025.</t>
+  </si>
+  <si>
+    <t>31 tháng 12 năm 2025.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1 Điều 39 Nghị định 106/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t>Đối với căn hộ của nhà chung cư (nhóm F1.3) có chiều cao PCCC không quá 100 m, được phép bố trí đầu phun sprinkler của hệ thống chữa cháy tự động bằng nước ở vị trí nào thay cho việc bảo vệ toàn bộ căn hộ?</t>
+  </si>
+  <si>
+    <t>Ngoài hành lang chung.</t>
+  </si>
+  <si>
+    <t>Tại cửa căn hộ (lắp đặt tại vị trí bên trong căn hộ).</t>
+  </si>
+  <si>
+    <t>Trong buồng thang bộ thoát nạn.</t>
+  </si>
+  <si>
+    <t>Ngoài ban công hoặc lô gia.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 1.5.12 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Theo QCVN 10:2025/BCA, bình chữa cháy trang bị tại cơ sở phải được bảo dưỡng định kỳ với tần suất tối thiểu là bao lâu?</t>
+  </si>
+  <si>
+    <t>Ít nhất 03 tháng một lần.</t>
+  </si>
+  <si>
+    <t>Ít nhất 06 tháng một lần.</t>
+  </si>
+  <si>
+    <t>Ít nhất 09 tháng một lần.</t>
+  </si>
+  <si>
+    <t>Ít nhất 12 tháng một lần.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 1.5.13 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Đối với công trình đang thi công xây dựng, bán kính bảo vệ tối đa của bình chữa cháy xách tay loại ABC (trang bị tại nơi dễ thấy, dễ lấy) được quy định là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>15 m.</t>
+  </si>
+  <si>
+    <t>20 m.</t>
+  </si>
+  <si>
+    <t>25 m.</t>
+  </si>
+  <si>
+    <t>30 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 2.6.5 1.5.12 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Nhà và công trình có chiều cao PCCC lớn hơn 28 m (hoặc nhà có chiều sâu của sàn tầng hầm dưới cùng lớn hơn 9 m) BẮT BUỘC phải bố trí hệ thống họng chờ cấp nước DN65 của đường ống khô ở vị trí nào cho lực lượng chữa cháy chuyên nghiệp?</t>
+  </si>
+  <si>
+    <t>Sát mép bãi đỗ xe chữa cháy ngoài nhà.</t>
+  </si>
+  <si>
+    <t>Trên mái nhà gần lối thoát nạn.</t>
+  </si>
+  <si>
+    <t>Tại các sảnh thang máy chữa cháy hoặc trong các khoang đệm của buồng thang bộ không nhiễm khói.</t>
+  </si>
+  <si>
+    <t>Tại giữa hành lang thoát nạn của tất cả các tầng.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 2.4.4 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Đèn chiếu sáng sự cố trang bị tại công trình đang thi công xây dựng phải đảm bảo độ rọi theo phương nằm ngang trên mặt sàn không được nhỏ hơn mức nào sau đây?</t>
+  </si>
+  <si>
+    <t>0,5 lux.</t>
+  </si>
+  <si>
+    <t>1,0 lux.</t>
+  </si>
+  <si>
+    <t>1,5 lux.</t>
+  </si>
+  <si>
+    <t>2,0 lux.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 2.2.3 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Theo quy định về lắp đặt hệ thống họng nước chữa cháy trong nhà, các họng nước chữa cháy phải được lắp đặt sao cho miệng họng nằm ở độ cao bao nhiêu so với mặt sàn?</t>
+  </si>
+  <si>
+    <t>1,00 m ± 0,10 m.</t>
+  </si>
+  <si>
+    <t>1,20 m ± 0,15 m.</t>
+  </si>
+  <si>
+    <t>1,25 m ± 0,20 m.</t>
+  </si>
+  <si>
+    <t>1,50 m ± 0,15 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: H.2.12 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Khi tính toán thiết kế trạm bơm cấp nước chữa cháy, nếu cần từ 01 đến 03 máy bơm chữa cháy chính thì quy định về máy bơm dự phòng như thế nào?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc phải có máy bơm dự phòng.</t>
+  </si>
+  <si>
+    <t>Phải có ít nhất 01 máy bơm dự phòng.</t>
+  </si>
+  <si>
+    <t>Phải có ít nhất 02 máy bơm dự phòng.</t>
+  </si>
+  <si>
+    <t>Số lượng máy bơm dự phòng phải bằng số lượng máy bơm chính.</t>
+  </si>
+  <si>
+    <t>Căn cứ: H.3.1 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Tín hiệu âm thanh của hệ thống loa thông báo và hướng dẫn thoát nạn (báo cháy) phải đảm bảo mức âm thanh tổng thể như thế nào?</t>
+  </si>
+  <si>
+    <t>Không thấp hơn 65 dBA ở khoảng cách 3m và không quá 100 dBA.</t>
+  </si>
+  <si>
+    <t>Không thấp hơn 75 dBA ở khoảng cách 3m và không quá 120 dBA ở bất kỳ vị trí nào.</t>
+  </si>
+  <si>
+    <t>Không thấp hơn 85 dBA ở khoảng cách 3m và không quá 130 dBA.</t>
+  </si>
+  <si>
+    <t>Không thấp hơn 90 dBA ở khoảng cách 3m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: H.4 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Theo quy định, 01 bộ dụng cụ phá dỡ thô sơ tối thiểu trang bị cho nhà và công trình bao gồm các thiết bị nào sau đây?</t>
+  </si>
+  <si>
+    <t>Rìu, cưa tay, búa, kìm.</t>
+  </si>
+  <si>
+    <t>Rìu, xà beng, búa, kìm cộng lực.</t>
+  </si>
+  <si>
+    <t>Máy cắt cầm tay, xà beng, búa, kìm.</t>
+  </si>
+  <si>
+    <t>Máy khoan, rìu, búa, kìm cộng lực.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Phụ lục E QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Đối với bình chữa cháy tự động kích hoạt lắp đặt treo trên trần nhà, khoảng cách từ bộ phận cảm biến nhiệt đến trần nhà được quy định tối đa là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Không quá 20 cm.</t>
+  </si>
+  <si>
+    <t>Không quá 30 cm.</t>
+  </si>
+  <si>
+    <t>Không quá 40 cm.</t>
+  </si>
+  <si>
+    <t>Không quá 50 cm.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 2.5.4 QCVN 10:2025/BCA.</t>
+  </si>
+  <si>
+    <t>Theo TCVN 7568-14:2025, một vùng phát hiện cháy trong nhà, công trình được giới hạn diện tích sàn liên tục lớn nhất là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>1.000 m²</t>
+  </si>
+  <si>
+    <t>1.500 m²</t>
+  </si>
+  <si>
+    <t>2.000 m²</t>
+  </si>
+  <si>
+    <t>2.500 m²</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.7.2.1 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Đối với các trần phẳng, khoảng cách tối đa giữa các đầu báo cháy khói kiểu điểm được quy định là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>7,2 m</t>
+  </si>
+  <si>
+    <t>8,5 m</t>
+  </si>
+  <si>
+    <t>9,0 m</t>
+  </si>
+  <si>
+    <t>10,2 m</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.9.1.1.2 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Khoảng cách từ đầu báo cháy khói đến mép ngoài gần nhất của cửa cấp không khí KHÔNG được nhỏ hơn mức nào sau đây?</t>
+  </si>
+  <si>
+    <t>0,3 m</t>
+  </si>
+  <si>
+    <t>0,4 m</t>
+  </si>
+  <si>
+    <t>0,5 m</t>
+  </si>
+  <si>
+    <t>0,6 m</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.9.1.1.4 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Khi thiết kế hệ thống báo cháy, hộp nút ấn báo cháy phải được lắp đặt ở độ cao bao nhiêu tính từ mặt đường đi lại?</t>
+  </si>
+  <si>
+    <t>(1,2 ± 0,2) m</t>
+  </si>
+  <si>
+    <t>(1,4 ± 0,2) m</t>
+  </si>
+  <si>
+    <t>(1,5 ± 0,2) m</t>
+  </si>
+  <si>
+    <t>(1,6 ± 0,2) m</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.10.4 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Khoảng cách tối đa giữa các hộp nút ấn báo cháy trên đường đi di chuyển là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>30 m</t>
+  </si>
+  <si>
+    <t>40 m</t>
+  </si>
+  <si>
+    <t>45 m</t>
+  </si>
+  <si>
+    <t>50 m</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.10.3 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Đối với thiết bị báo cháy bằng âm thanh (trừ các khu vực đặc thù như phòng ngủ), mức cường độ âm thanh phải đảm bảo trong khoảng nào?</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 60 dBA và không lớn hơn 100 dBA</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 65 dBA và không lớn hơn 105 dBA</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 70 dBA và không lớn hơn 110 dBA</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 75 dBA và không lớn hơn 115 dBA</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.11.2.1 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Đối với trung tâm báo cháy, dung lượng của ắc quy dự phòng phải bảo đảm cho thiết bị hoạt động tối thiểu trong thời gian bao lâu ở chế độ thường trực và khi có cháy?</t>
+  </si>
+  <si>
+    <t>12 h ở chế độ thường trực và 30 min khi có cháy.</t>
+  </si>
+  <si>
+    <t>24 h ở chế độ thường trực và 30 min khi có cháy.</t>
+  </si>
+  <si>
+    <t>24 h ở chế độ thường trực và 60 min khi có cháy.</t>
+  </si>
+  <si>
+    <t>48 h ở chế độ thường trực và 60 min khi có cháy.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.13 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Yêu cầu về không gian làm việc phía trước mặt tủ trung tâm báo cháy tối thiểu là bao nhiêu để thuận tiện thao tác?</t>
+  </si>
+  <si>
+    <t>0,8 m</t>
+  </si>
+  <si>
+    <t>1,0 m</t>
+  </si>
+  <si>
+    <t>1,2 m</t>
+  </si>
+  <si>
+    <t>1,5 m</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.12.3 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Tiết diện lõi đồng của cáp và dây tín hiệu đường cáp trục chính của hệ thống báo cháy không được nhỏ hơn mức nào để bảo đảm yêu cầu sụt áp?</t>
+  </si>
+  <si>
+    <t>0,5 mm²</t>
+  </si>
+  <si>
+    <t>0,75 mm²</t>
+  </si>
+  <si>
+    <t>1,0 mm²</t>
+  </si>
+  <si>
+    <t>1,5 mm²</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.14.5 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Đối với các bề mặt trần phẳng, khoảng cách lớn nhất giữa các đầu báo cháy nhiệt kiểu điểm là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>5,1 m</t>
+  </si>
+  <si>
+    <t>14,4 m</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.9.2.1.2 TCVN 7568-14:2025.</t>
+  </si>
+  <si>
+    <t>Theo TCVN 7336:2021, áp suất làm việc tối đa của các đầu phun nước và bọt thông thường không được vượt quá bao nhiêu?</t>
+  </si>
+  <si>
+    <t>0,8 MPa.</t>
+  </si>
+  <si>
+    <t>1,0 MPa.</t>
+  </si>
+  <si>
+    <t>1,2 MPa.</t>
+  </si>
+  <si>
+    <t>1,5 MPa.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.1.4 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Đối với hệ thống Sprinkler khô, thời gian đáp ứng của hệ thống (kể từ khi đầu phun được kích hoạt tới khi nước bắt đầu được phun ra) tối đa là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>60 giây.</t>
+  </si>
+  <si>
+    <t>90 giây.</t>
+  </si>
+  <si>
+    <t>120 giây.</t>
+  </si>
+  <si>
+    <t>180 giây.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.2.4 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Khoảng cách từ tâm phần tử nhạy cảm với nhiệt của đầu phun Sprinkler đến mặt phẳng trần (mái) thông thường phải nằm trong khoảng nào?</t>
+  </si>
+  <si>
+    <t>Từ 0,05 m đến 0,20 m.</t>
+  </si>
+  <si>
+    <t>Từ 0,08 m đến 0,30 m.</t>
+  </si>
+  <si>
+    <t>Từ 0,10 m đến 0,40 m.</t>
+  </si>
+  <si>
+    <t>Từ 0,15 m đến 0,50 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.2.12 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Một cụm bảo vệ của hệ thống Sprinkler thông thường (không sử dụng công tắc dòng chảy phân vùng hoặc đầu phun có giám sát) không được thiết kế vượt quá bao nhiêu đầu phun?</t>
+  </si>
+  <si>
+    <t>500 đầu phun.</t>
+  </si>
+  <si>
+    <t>800 đầu phun.</t>
+  </si>
+  <si>
+    <t>1.000 đầu phun.</t>
+  </si>
+  <si>
+    <t>1.200 đầu phun.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.2.3 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Đối với hệ thống có dưới 100 đầu phun Sprinkler, quy định bắt buộc phải dự trữ tại cơ sở tối thiểu bao nhiêu đầu phun cùng loại?</t>
+  </si>
+  <si>
+    <t>02 đầu phun.</t>
+  </si>
+  <si>
+    <t>03 đầu phun.</t>
+  </si>
+  <si>
+    <t>05 đầu phun.</t>
+  </si>
+  <si>
+    <t>10 đầu phun.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.1.12 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Để bảo đảm yêu cầu xả đọng và thoát nước, đường ống chính và đường ống phân phối có đường kính danh định từ DN50 trở lên phải được lắp đặt với độ dốc tối thiểu là bao nhiêu về phía thiết bị thoát nước?</t>
+  </si>
+  <si>
+    <t>0,5%</t>
+  </si>
+  <si>
+    <t>1,0%</t>
+  </si>
+  <si>
+    <t>1,5%</t>
+  </si>
+  <si>
+    <t>2,0%</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.5.11 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Khi sử dụng công tắc dòng chảy trong bộ điều khiển để truyền tín hiệu kích hoạt bơm chữa cháy, nhằm hạn chế báo động sai, cần phải cài đặt thời gian trễ trong khoảng bao lâu?</t>
+  </si>
+  <si>
+    <t>Từ 1 giây đến 3 giây.</t>
+  </si>
+  <si>
+    <t>Từ 3 giây đến 5 giây.</t>
+  </si>
+  <si>
+    <t>Từ 5 giây đến 10 giây.</t>
+  </si>
+  <si>
+    <t>Không cài đặt thời gian trễ.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.6.7 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Khoảng cách tối thiểu theo phương ngang giữa các đầu phun Sprinkler với nhau trên cùng một mạng đường ống được quy định là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 1,0 m.</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 1,2 m.</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 1,5 m.</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 2,0 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.2.22 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Khi tiến hành thử nghiệm, đường ống của hệ thống chữa cháy tự động bằng nước, bọt phải chịu được áp suất thử nghiệm (Pth) bằng bao nhiêu so với áp suất làm việc tối đa (Plv.max)?</t>
+  </si>
+  <si>
+    <t>Pth = 1,1 Plv.max</t>
+  </si>
+  <si>
+    <t>Pth = 1,25 Plv.max</t>
+  </si>
+  <si>
+    <t>Pth = 1,5 Plv.max</t>
+  </si>
+  <si>
+    <t>Pth = 2,0 Plv.max</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.5.13 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Nhiệt độ không khí bên trong phòng của trạm bơm nước chữa cháy bắt buộc phải được duy trì trong khoảng nào?</t>
+  </si>
+  <si>
+    <t>Từ 0 °C đến 40 °C.</t>
+  </si>
+  <si>
+    <t>Từ 5 °C đến 40 °</t>
+  </si>
+  <si>
+    <t>C. Từ 10 °C đến 45 °C.</t>
+  </si>
+  <si>
+    <t>Từ 15 °C đến 35 °C.</t>
+  </si>
+  <si>
+    <t>Căn cứ: 5.8.7 TCVN 7336:2021.</t>
+  </si>
+  <si>
+    <t>Theo QCVN 01:2020/BCT, quy định nào sau đây là ĐÚNG đối với việc lắp đặt bể chứa xăng dầu tại cửa hàng xăng dầu trên mặt đất?</t>
+  </si>
+  <si>
+    <t>Được phép lắp đặt nổi nếu có hệ thống đê bao ngăn cháy.</t>
+  </si>
+  <si>
+    <t>Không được lắp đặt bể chứa xăng dầu nổi trên mặt đất.</t>
+  </si>
+  <si>
+    <t>Được phép lắp đặt trong hoặc dưới các gian bán hàng nếu có vách ngăn cháy.</t>
+  </si>
+  <si>
+    <t>Được phép lắp nổi nhưng phải cách xa gian bán hàng tối thiểu 10 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b, Khoản 1, Điều 8 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Đường và bãi đỗ xe dành cho xe ra vào mua hàng và nhập hàng tại cửa hàng xăng dầu trên mặt đất phải đảm bảo chiều rộng thiết kế tối thiểu là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Chiều rộng một làn xe đi không nhỏ hơn 3,0 m; đường hai làn xe đi không nhỏ hơn 5,5 m.</t>
+  </si>
+  <si>
+    <t>Chiều rộng một làn xe đi không nhỏ hơn 3,5 m; đường hai làn xe đi không nhỏ hơn 6,0 m.</t>
+  </si>
+  <si>
+    <t>Chiều rộng một làn xe đi không nhỏ hơn 3,5 m; đường hai làn xe đi không nhỏ hơn 6,5 m.</t>
+  </si>
+  <si>
+    <t>Chiều rộng một làn xe đi không nhỏ hơn 4,0 m; đường hai làn xe đi không nhỏ hơn 7,0 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm c, Khoản 6, Điều 6 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Đảo bơm (nơi lắp đặt cột bơm xăng dầu) tại cửa hàng xăng dầu trên mặt đất phải được thiết kế với kích thước như thế nào?</t>
+  </si>
+  <si>
+    <t>Cao độ cao hơn mặt bằng bãi đỗ xe ít nhất 0,15 m và chiều rộng không nhỏ hơn 1,0 m.</t>
+  </si>
+  <si>
+    <t>Cao độ cao hơn mặt bằng bãi đỗ xe ít nhất 0,20 m và chiều rộng không nhỏ hơn 1,2 m.</t>
+  </si>
+  <si>
+    <t>Cao độ cao hơn mặt bằng bãi đỗ xe ít nhất 0,10 m và chiều rộng không nhỏ hơn 0,8 m.</t>
+  </si>
+  <si>
+    <t>Cao độ cao hơn mặt bằng bãi đỗ xe ít nhất 0,15 m và chiều rộng không nhỏ hơn 1,2 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b, Khoản 1, Điều 9 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Đường ống công nghệ trong cửa hàng xăng dầu phải được chế tạo từ vật liệu chịu xăng dầu và không cháy. Đường kính trong của ống tối thiểu phải đạt bao nhiêu?</t>
+  </si>
+  <si>
+    <t>25 mm.</t>
+  </si>
+  <si>
+    <t>32 mm.</t>
+  </si>
+  <si>
+    <t>40 mm.</t>
+  </si>
+  <si>
+    <t>50 mm.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1, Điều 10 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Đối với hệ thống van thở của bể chứa xăng dầu, đường kính trong của ống nối từ bể tới van thở được quy định không được nhỏ hơn kích thước nào sau đây?</t>
+  </si>
+  <si>
+    <t>65 mm.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b, Khoản 9, Điều 10 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Việc nhập xăng dầu vào bể chứa tại cửa hàng xăng dầu trên mặt đất phải sử dụng phương pháp nào và khoảng cách từ đầu đường ống nhập đến đáy bể được quy định ra sao?</t>
+  </si>
+  <si>
+    <t>Phương pháp nhập hở; cách đáy bể không quá 15 cm.</t>
+  </si>
+  <si>
+    <t>Phương pháp nhập kín; cách đáy bể không quá 20 cm.</t>
+  </si>
+  <si>
+    <t>Phương pháp nhập kín; cách đáy bể ít nhất 25 cm.</t>
+  </si>
+  <si>
+    <t>Tùy chọn phương pháp nhập; ống nhập phải chạm sát đáy bể.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 5, Điều 10 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Theo phân cấp vùng nguy hiểm cháy nổ tại Phụ lục I của QCVN 01:2020/BCT, "Vùng nguy hiểm cấp Z1 (Zone 1)" được định nghĩa là gì?</t>
+  </si>
+  <si>
+    <t>Vùng mà môi trường khí nổ xuất hiện tích tụ một cách thường xuyên, liên tục trong thời gian dài.</t>
+  </si>
+  <si>
+    <t>Vùng mà môi trường khí nổ có thể xuất hiện nhưng không thường xuyên trong các điều kiện hoạt động bình thường.</t>
+  </si>
+  <si>
+    <t>Vùng mà môi trường khí nổ không có khả năng xuất hiện trong các điều kiện hoạt động bình thường.</t>
+  </si>
+  <si>
+    <t>Vùng không tồn tại các chất dễ cháy dưới dạng khí hoặc hơi.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 1, Phụ lục I QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Cửa hàng xăng dầu tiếp giáp với công trình xây dựng khác (không phải là tường ngăn cháy) phải có tường bao kín bằng vật liệu không cháy với chiều cao tối thiểu là bao nhiêu (tính từ cốt nền sân bên trong cửa hàng)?</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 2,2 m.</t>
+  </si>
+  <si>
+    <t>Không nhỏ hơn 2,5 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm d, Khoản 6, Điều 6 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Khi lắp đặt các bình chữa cháy tại cửa hàng xăng dầu, nếu treo trên tường hoặc cột thì khoảng cách từ mặt nền, sàn đến tay cầm của bình không được lớn hơn bao nhiêu?</t>
+  </si>
+  <si>
+    <t>1,00 m.</t>
+  </si>
+  <si>
+    <t>1,25 m.</t>
+  </si>
+  <si>
+    <t>1,50 m.</t>
+  </si>
+  <si>
+    <t>1,75 m.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Khoản 7, Điều 12 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Hệ thống nối đất chống sét đánh thẳng cho các hạng mục xây dựng trong cửa hàng xăng dầu phải có trị số điện trở nối đất tối đa là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Không vượt quá 1 Ω.</t>
+  </si>
+  <si>
+    <t>Không vượt quá 4 Ω.</t>
+  </si>
+  <si>
+    <t>Không vượt quá 10 Ω.</t>
+  </si>
+  <si>
+    <t>Không vượt quá 15 Ω.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm e, Khoản 1, Điều 11 QCVN 01:2020/BCT.</t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm d, Khoản 4, Điều 6 Nghị định 105/2025/NĐ-CP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Căn cứ: Điểm a, Khoản 3 Điều 11 Luật PCCC số 55/2024/QH15 </t>
+  </si>
+  <si>
+    <t>Căn cứ: Điểm b và d, Khoản 2 Điều 21 Luật PCCC số 55/2024/QH15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,17 +1722,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF303030"/>
-      <name val="Google Sans Text"/>
     </font>
   </fonts>
   <fills count="3">
@@ -218,7 +1759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,13 +1770,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -247,12 +1787,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -294,72 +1830,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -367,55 +1845,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -424,13 +1862,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -464,24 +1902,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -507,7 +1934,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -536,8 +1963,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H101"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -546,7 +1973,7 @@
     <col min="8" max="8" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,12 +1999,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>43</v>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -592,13 +2019,13 @@
         <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="43.2">
+    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -618,13 +2045,13 @@
         <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.8">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -632,1248 +2059,2547 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="28.8">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28.8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="28.8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="43.2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="28.8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28.8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28.8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="28.8">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="28.8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="28.8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="28.8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="28.8">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="28.8">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>11</v>
+        <v>137</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="28.8">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="28.8">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>29</v>
+        <v>148</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="28.8">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>8</v>
+        <v>153</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="28.8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="28.8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="28.8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>30</v>
+        <v>177</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="28.8">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>8</v>
+        <v>181</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>39</v>
+        <v>178</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>11</v>
+        <v>182</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>12</v>
+        <v>183</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="43.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>16</v>
+        <v>178</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>17</v>
+        <v>179</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="28.8">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>10</v>
+        <v>186</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>11</v>
+        <v>187</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="28.8">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>22</v>
+        <v>191</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>23</v>
+        <v>192</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="28.8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>30</v>
+        <v>198</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="28.8">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>8</v>
+        <v>202</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="43.2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>14</v>
+        <v>208</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>15</v>
+        <v>209</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>17</v>
+        <v>211</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="28.8">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>10</v>
+        <v>211</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>11</v>
+        <v>212</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>12</v>
+        <v>215</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="28.8">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>25</v>
+        <v>212</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="28.8">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>31</v>
+        <v>224</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="28.8">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>41</v>
+        <v>209</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>11</v>
+        <v>211</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>12</v>
+        <v>212</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="43.2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>15</v>
+        <v>211</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>16</v>
+        <v>212</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="28.8">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>19</v>
+        <v>231</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>10</v>
+        <v>232</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>11</v>
+        <v>233</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>12</v>
+        <v>234</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="28.8">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>22</v>
+        <v>237</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>23</v>
+        <v>238</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>25</v>
+        <v>240</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="28.8">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>29</v>
+        <v>243</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>30</v>
+        <v>244</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>32</v>
+        <v>246</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="28.8">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>8</v>
+        <v>248</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>42</v>
+        <v>249</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>11</v>
+        <v>251</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="43.2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>16</v>
+        <v>255</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>17</v>
+        <v>256</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>18</v>
+        <v>257</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="28.8">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>19</v>
+        <v>259</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>10</v>
+        <v>260</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>11</v>
+        <v>261</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>20</v>
+        <v>263</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="28.8">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>22</v>
+        <v>264</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>23</v>
+        <v>265</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>24</v>
+        <v>266</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>25</v>
+        <v>267</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>26</v>
+        <v>268</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="28.8">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>28</v>
+        <v>269</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>29</v>
+        <v>270</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>30</v>
+        <v>271</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>31</v>
+        <v>272</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>32</v>
+        <v>273</v>
       </c>
       <c r="G51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>33</v>
+      <c r="H53" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>557</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/questions.xlsx
+++ b/questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nguyen\Downloads\pccc-main-fixed\pccc-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/334d56c47349e4dc/Desktop/pccc-main/pccc-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5151F5A4-AB66-4682-89B6-3D797D8F39E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5151F5A4-AB66-4682-89B6-3D797D8F39E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9968F80F-1606-4016-9099-1586EF088A70}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NganHangCauHoi" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="584">
   <si>
     <t>STT</t>
   </si>
@@ -1770,6 +1770,9 @@
   </si>
   <si>
     <t xml:space="preserve">Nộp phạt hành chính để duy trì hoạt động. </t>
+  </si>
+  <si>
+    <t>Từ - 30 °C đến + 5 °C</t>
   </si>
 </sst>
 </file>
@@ -1995,14 +1998,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="13.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.625" style="1" customWidth="1"/>
-    <col min="4" max="7" width="30.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.59765625" style="1" customWidth="1"/>
+    <col min="4" max="7" width="30.59765625" style="2" customWidth="1"/>
     <col min="8" max="8" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="49.19921875" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2035,7 +2038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="47.25">
+    <row r="2" spans="1:9" ht="46.8">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2064,7 +2067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5">
+    <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2093,7 +2096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="47.25">
+    <row r="4" spans="1:9" ht="46.8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2122,7 +2125,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.5">
+    <row r="5" spans="1:9" ht="31.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2151,7 +2154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="47.25">
+    <row r="6" spans="1:9" ht="46.8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2180,7 +2183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="47.25">
+    <row r="7" spans="1:9" ht="46.8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2209,7 +2212,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="31.5">
+    <row r="8" spans="1:9" ht="31.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2238,7 +2241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="31.5">
+    <row r="9" spans="1:9" ht="31.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2296,7 +2299,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="31.5">
+    <row r="11" spans="1:9" ht="31.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2325,7 +2328,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="31.5">
+    <row r="12" spans="1:9" ht="46.8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2354,7 +2357,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="47.25">
+    <row r="13" spans="1:9" ht="46.8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2383,7 +2386,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="31.5">
+    <row r="14" spans="1:9" ht="46.8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2412,7 +2415,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="31.5">
+    <row r="15" spans="1:9" ht="31.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2441,7 +2444,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="31.5">
+    <row r="16" spans="1:9" ht="31.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2470,7 +2473,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="31.5">
+    <row r="17" spans="1:9" ht="31.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2499,7 +2502,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="31.5">
+    <row r="18" spans="1:9" ht="31.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2528,7 +2531,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="31.5">
+    <row r="19" spans="1:9" ht="31.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2557,7 +2560,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="31.5">
+    <row r="20" spans="1:9" ht="31.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2586,7 +2589,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="47.25">
+    <row r="21" spans="1:9" ht="46.8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2615,7 +2618,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="47.25">
+    <row r="22" spans="1:9" ht="46.8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4398,7 +4401,7 @@
         <v>413</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>413</v>
+        <v>583</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>414</v>
@@ -4938,13 +4941,14 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
